--- a/registration_forms/028_entrepreneurial_networking_event_registration_form--registration_forms.xlsx
+++ b/registration_forms/028_entrepreneurial_networking_event_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>business-name</t>
+          <t>Business Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>job-title</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -667,13 +667,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -690,30 +690,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select-multiple</t>
+          <t>Select Multiple</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>select-one</t>
+          <t>Select One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,40 +841,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +887,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Select One 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -910,17 +910,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>select-one-2</t>
+          <t>Select Multiple 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -933,17 +933,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>select-multiple-2</t>
+          <t>Select One 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>select-multiple-3</t>
+          <t>Select Multiple 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -979,113 +979,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>select-multiple-4</t>
+          <t>Select One 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>select-multiple-5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>select-one</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>select-one-2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>select-multiple</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1102,10 +1010,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1140,7 +1048,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>category_a</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1065,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>category_b</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1082,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>category_c</t>
+          <t>Category C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1099,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1116,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1133,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1150,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1167,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,7 +1191,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,7 +1208,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1225,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,7 +1242,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1259,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1276,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1293,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1310,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1327,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,7 +1344,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1453,7 +1361,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1470,7 +1378,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1487,7 +1395,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1496,40 +1404,6 @@
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
